--- a/계산모델_엑셀/실험런시트.xlsx
+++ b/계산모델_엑셀/실험런시트.xlsx
@@ -589,7 +589,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>182µm</t>
+          <t>158µm</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="G5" s="5" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="I5" s="6">
         <f>IFERROR(G5/H5,"")</f>
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>182µm</t>
+          <t>158µm</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="G6" s="5" t="n"/>
       <c r="H6" s="4" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="I6" s="6">
         <f>IFERROR(G6/H6,"")</f>
@@ -768,7 +768,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>고정: W=4W, Acquisition 표준세트</t>
+          <t>이 단계는 W=4W로 고정(얇은 범프 기준값). W 자체의 최적화는 PhaseW에서 별도 진행 / Acquisition 표준세트</t>
         </is>
       </c>
     </row>
@@ -940,11 +940,11 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>182µm</t>
+          <t>158µm</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>1</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="4" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="H7" s="6">
         <f>IFERROR(F7/G7,"")</f>
@@ -972,7 +972,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>60kV 기존 40건과 이어 기울기 확정</t>
+          <t>기존 60kV 데이터와 이어붙여 158µm 기울기 확정(158µm은 실측 없어 2점 직선)</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,11 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>182µm</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>(산출 kV*)</t>
-        </is>
+          <t>158µm</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>63</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>1</v>
@@ -1000,7 +998,7 @@
       </c>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="4" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="H8" s="6">
         <f>IFERROR(F8/G8,"")</f>
@@ -1018,7 +1016,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>kV*가 60±1 밖일 때만</t>
+          <t>60·63kV 2점으로 158µm 최적 kV 확정</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1060,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>고정: W=4W, kV=B0에서 확정한 값 유지</t>
+          <t>고정: W=4W(26µm은 W에 둔감 — 얇아 내부도 밝음), kV=B0에서 확정한 값 유지</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1672,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>182µm</t>
+          <t>158µm</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1690,7 +1688,7 @@
       </c>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="4" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="H6" s="6">
         <f>IFERROR(F6/G6,"")</f>
@@ -1708,7 +1706,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>R완화 → tact ~4배 단축 입증</t>
+          <t>R 완화 → 검사시간 약 4배 단축 입증 / W는 PhaseW 최적값 사용</t>
         </is>
       </c>
     </row>
@@ -1723,7 +1721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1764,24 +1762,24 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>182µm 기울기 s</t>
+          <t>158µm 기울기 s (%p/kV)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(Q_A2 − 101.7%)/(62−60)</t>
+          <t>(Q_A3 − Q_A2) / (63 − 60)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>182µm kV*</t>
+          <t>158µm 최적 kV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60 + (100%−101.7%)/s</t>
+          <t>직선상 측정직경/도면 = 100% 가 되는 kV</t>
         </is>
       </c>
     </row>
@@ -1818,6 +1816,18 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>각 런 tact를 (1/R², F)에 회귀 → 계수 2개</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>W 최적값 (158µm)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PhaseW: 깜빡임 void=0 &amp; void% 반복편차(σ) 최소가 되는 W. 얇은 26µm는 4W로 둔감→고정</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1871,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>고정: kV*(PhaseA 결과), R(모델값), F32, 같은 die·AOI·범프 추적 | 판정: 깜빡임void 수·void%σ·수렴 + 가드(경계폭·Q_dia)</t>
+          <t>고정: kV*(PhaseA 결과)·R(모델값)·F32, 같은 die·AOI·범프 추적 | W는 고정이 아니라 최적화 대상 — 판정: 깜빡임void 수·void%σ·수렴 + 가드(경계폭·Q_dia)</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/실험런시트.xlsx
+++ b/계산모델_엑셀/실험런시트.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhaseC_검증" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분석_자동계산" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PhaseW_Power" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shot_타일일관성" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,7 +47,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +67,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -105,6 +111,12 @@
     <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -580,6 +592,16 @@
           <t>메모</t>
         </is>
       </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>검사범프수</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>shot수</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -629,6 +651,12 @@
           <t>현행 운용 기준선</t>
         </is>
       </c>
+      <c r="P5" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -678,6 +706,12 @@
           <t>P1과 매칭률 비교</t>
         </is>
       </c>
+      <c r="P6" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -726,6 +760,12 @@
         <is>
           <t>PhaseB 신규취득 결과와 비교</t>
         </is>
+      </c>
+      <c r="P7" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -739,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -843,6 +883,16 @@
           <t>메모</t>
         </is>
       </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>검사범프수</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>shot수</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -887,6 +937,12 @@
           <t>예측 kV* 검증. 매칭실패 시 58.5 재시도</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>50</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -931,6 +987,12 @@
           <t>(A1 매칭실패 시에만)</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>50</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -975,6 +1037,12 @@
           <t>기존 60kV 데이터와 이어붙여 158µm 기울기 확정(158µm은 실측 없어 2점 직선)</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>50</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1018,6 +1086,12 @@
         <is>
           <t>60·63kV 2점으로 158µm 최적 kV 확정</t>
         </is>
+      </c>
+      <c r="O8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1064,6 +1138,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>★일관성 규칙: R을 넓게 바꾸므로, '가장 작은 R(0.2)에서도 1 shot에 들어오는 중앙 ~50개 범프'만 고정 추적한다. 그러면 모든 R이 1 shot=동일 범프가 되어 shot 수 교란이 사라진다. void%는 각 범프 로컬 픽셀로 계산.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1133,6 +1214,16 @@
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>메모</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>검사범프수</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>shot수</t>
         </is>
       </c>
     </row>
@@ -1181,6 +1272,12 @@
           <t>R0.2에서 Q≈100% 만들기 → 기준 void%</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>50</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1227,6 +1324,12 @@
           <t>N곡선</t>
         </is>
       </c>
+      <c r="O6" t="n">
+        <v>50</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1273,6 +1376,12 @@
           <t>N곡선 (A1과 병합 가능)</t>
         </is>
       </c>
+      <c r="O7" t="n">
+        <v>50</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1319,6 +1428,12 @@
           <t>N곡선</t>
         </is>
       </c>
+      <c r="O8" t="n">
+        <v>50</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1365,6 +1480,12 @@
           <t>반복 — 재현성</t>
         </is>
       </c>
+      <c r="O9" t="n">
+        <v>50</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1411,6 +1532,12 @@
           <t>Frame 하향 — void%σ, tact</t>
         </is>
       </c>
+      <c r="O10" t="n">
+        <v>50</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1457,6 +1584,12 @@
           <t>Frame 상향 — void%σ, tact</t>
         </is>
       </c>
+      <c r="O11" t="n">
+        <v>50</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1496,6 +1629,12 @@
         <is>
           <t>26px 아래 두번째 점(13px) — 취득R 상한 검증</t>
         </is>
+      </c>
+      <c r="O12" t="n">
+        <v>50</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1509,7 +1648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1613,6 +1752,16 @@
           <t>메모</t>
         </is>
       </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>검사범프수</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>shot수</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1663,6 +1812,13 @@
           <t>품질+시간 최종 확인</t>
         </is>
       </c>
+      <c r="O5" t="n">
+        <v>300</v>
+      </c>
+      <c r="P5">
+        <f>ROUNDUP(300/50,0) 예상</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1708,6 +1864,12 @@
         <is>
           <t>R 완화 → 검사시간 약 4배 단축 입증 / W는 PhaseW 최적값 사용</t>
         </is>
+      </c>
+      <c r="O6" t="n">
+        <v>300</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2269,4 +2431,338 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Shot 타일 일관성 대조 — '6번 찍기 vs 1번 찍기'가 결과를 바꾸는지 직접 검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>질문: R0.2로 6 shot(타일) 찍은 것과 R1로 1 shot 찍은 것을 그대로 비교해도 되나? → R 효과와 shot(타일) 효과가 섞이지 않게, R을 고정하고 shot 수만 바꿔 타일 자체의 영향을 분리한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>자재</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>R(µm/px)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>kV</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Frame</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>목표범프</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>shot수(타일)</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>측정직경(µm)</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>nominal</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Q_dia(자동)</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>void%(범프별)</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>void%차이 vs 기준</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TB500M</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>32</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>300</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K5">
+        <f>IFERROR(I5/J5,"")</f>
+        <v/>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>기준(1 shot)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>단일 shot 기준값</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TB500M</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <f>IFERROR(I6/J6,"")</f>
+        <v/>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>S1과 범프별 비교</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>같은 R·같은 범프를 억지로 6타일로 → 타일 순수효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>158µm</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>32</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>W*</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>158</v>
+      </c>
+      <c r="K7">
+        <f>IFERROR(I7/J7,"")</f>
+        <v/>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>기준(1 shot)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>158µm</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>kV*</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>32</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>W*</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>158</v>
+      </c>
+      <c r="K8">
+        <f>IFERROR(I8/J8,"")</f>
+        <v/>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>S3과 범프별 비교</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>두꺼운 범프에서도 재확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>판정: S2−S1(및 S4−S3)의 '범프별 void% 차이'가 ε·p(예 ±0.8%p) 이내면 타일이 결과를 바꾸지 않음 → 6 shot 데이터와 1 shot 데이터를 함께 써도 일관성 유지. 초과하면 → 타일 경계·콘빔 가장자리 영향 존재 → 타일 겹침(≥1 pitch)·중앙 범프만 사용 규칙 적용, 서로 다른 shot수 데이터는 직접 비교 금지.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A11:N14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/계산모델_엑셀/실험런시트.xlsx
+++ b/계산모델_엑셀/실험런시트.xlsx
@@ -1134,7 +1134,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>고정: W=4W(26µm은 W에 둔감 — 얇아 내부도 밝음), kV=B0에서 확정한 값 유지</t>
+          <t>고정: W=4W(26µm은 W에 둔감), kV=B0에서 확정한 값 유지. Frame은 32/64/128(장비 F최소=32)</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="4" t="n">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Frame 하향 — void%σ, tact</t>
+          <t>Frame 상향(128) — void%σ, tact (장비 F최소=32라 하향 불가)</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D13" s="4" t="n">
         <v>1</v>
@@ -2424,7 +2424,7 @@
       <c r="M13" s="5" t="n"/>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>W·F 교환검증: (4W,F32)와 void% 비교</t>
+          <t>W·F 교환검증: 8W로 F 64→32 가능한지 (4W·F64와 void% 비교, F최소=32)</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2575,6 @@
       <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
         <v>26</v>
       </c>
@@ -2583,7 +2582,6 @@
         <f>IFERROR(I5/J5,"")</f>
         <v/>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>기준(1 shot)</t>
@@ -2626,7 +2624,6 @@
       <c r="H6" t="n">
         <v>6</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
         <v>26</v>
       </c>
@@ -2634,7 +2631,6 @@
         <f>IFERROR(I6/J6,"")</f>
         <v/>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>S1과 범프별 비교</t>
@@ -2679,7 +2675,6 @@
       <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
         <v>158</v>
       </c>
@@ -2687,13 +2682,11 @@
         <f>IFERROR(I7/J7,"")</f>
         <v/>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>기준(1 shot)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2728,7 +2721,6 @@
       <c r="H8" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
         <v>158</v>
       </c>
@@ -2736,7 +2728,6 @@
         <f>IFERROR(I8/J8,"")</f>
         <v/>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>S3과 범프별 비교</t>
